--- a/codes/EMPIRE/Data handler/reduced/Sets.xlsx
+++ b/codes/EMPIRE/Data handler/reduced/Sets.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10609"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D247F600-E85B-FD47-BA18-0B92E4F57D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAE940-E331-0E48-AF02-FCDB47A43B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" tabRatio="817" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="680" windowWidth="14400" windowHeight="17960" tabRatio="817" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">DirectionalLines!$A$1:$B$383</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">GeneratorsOfNode!$A$1:$B$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">GeneratorsOfTechnology!$A$1:$B$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">GeneratorsOfNode!$A$1:$B$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">GeneratorsOfTechnology!$A$1:$B$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LineTypeOfDirectionalLines!$A$1:$C$383</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Nodes!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">StorageOfNodes!$A$1:$B$69</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="112">
   <si>
     <t>Liginite existing</t>
   </si>
@@ -333,18 +333,6 @@
     <t>Waste</t>
   </si>
   <si>
-    <t>Wind_offshr_grounded</t>
-  </si>
-  <si>
-    <t>Wind_offshr_floating</t>
-  </si>
-  <si>
-    <t>Wind offshore grounded</t>
-  </si>
-  <si>
-    <t>Wind offshore floating</t>
-  </si>
-  <si>
     <t>Moray Firth</t>
   </si>
   <si>
@@ -391,6 +379,12 @@
   </si>
   <si>
     <t>OffshoreNode</t>
+  </si>
+  <si>
+    <t>Wind offshore</t>
+  </si>
+  <si>
+    <t>Wind_offshr</t>
   </si>
 </sst>
 </file>
@@ -2215,10 +2209,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B168" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C168" t="s">
         <v>82</v>
@@ -2226,10 +2220,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B169" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C169" t="s">
         <v>82</v>
@@ -2237,10 +2231,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B170" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C170" t="s">
         <v>82</v>
@@ -2248,10 +2242,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B171" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C171" t="s">
         <v>82</v>
@@ -2259,10 +2253,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B172" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C172" t="s">
         <v>82</v>
@@ -2270,10 +2264,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B173" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C173" t="s">
         <v>82</v>
@@ -2281,10 +2275,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B174" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C174" t="s">
         <v>82</v>
@@ -2292,10 +2286,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B175" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C175" t="s">
         <v>82</v>
@@ -2303,10 +2297,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B176" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C176" t="s">
         <v>82</v>
@@ -2314,10 +2308,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B177" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C177" t="s">
         <v>82</v>
@@ -2325,10 +2319,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B178" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C178" t="s">
         <v>82</v>
@@ -2336,10 +2330,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B179" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C179" t="s">
         <v>82</v>
@@ -2347,10 +2341,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B180" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C180" t="s">
         <v>82</v>
@@ -2358,10 +2352,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B181" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C181" t="s">
         <v>82</v>
@@ -2369,10 +2363,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B182" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C182" t="s">
         <v>82</v>
@@ -2380,10 +2374,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B183" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C183" t="s">
         <v>82</v>
@@ -2391,10 +2385,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B184" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C184" t="s">
         <v>82</v>
@@ -2402,10 +2396,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B185" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C185" t="s">
         <v>82</v>
@@ -2413,10 +2407,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B186" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C186" t="s">
         <v>82</v>
@@ -2424,10 +2418,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B187" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C187" t="s">
         <v>82</v>
@@ -2435,10 +2429,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B188" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C188" t="s">
         <v>82</v>
@@ -2446,10 +2440,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B189" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C189" t="s">
         <v>82</v>
@@ -2457,10 +2451,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B190" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C190" t="s">
         <v>82</v>
@@ -2468,10 +2462,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B191" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C191" t="s">
         <v>82</v>
@@ -2479,10 +2473,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B192" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C192" t="s">
         <v>82</v>
@@ -2490,10 +2484,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B193" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C193" t="s">
         <v>82</v>
@@ -2501,10 +2495,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B194" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C194" t="s">
         <v>82</v>
@@ -2512,10 +2506,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B195" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C195" t="s">
         <v>82</v>
@@ -2523,10 +2517,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B196" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C196" t="s">
         <v>82</v>
@@ -2534,10 +2528,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B197" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C197" t="s">
         <v>82</v>
@@ -2545,10 +2539,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B198" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C198" t="s">
         <v>82</v>
@@ -2556,10 +2550,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B199" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C199" t="s">
         <v>82</v>
@@ -2567,10 +2561,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B200" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C200" t="s">
         <v>82</v>
@@ -2578,10 +2572,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B201" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C201" t="s">
         <v>82</v>
@@ -2589,10 +2583,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B202" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C202" t="s">
         <v>82</v>
@@ -2600,10 +2594,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B203" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C203" t="s">
         <v>82</v>
@@ -2611,10 +2605,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B204" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C204" t="s">
         <v>82</v>
@@ -2622,10 +2616,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B205" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C205" t="s">
         <v>82</v>
@@ -2633,10 +2627,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B206" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C206" t="s">
         <v>82</v>
@@ -2644,10 +2638,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B207" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C207" t="s">
         <v>82</v>
@@ -2655,10 +2649,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B208" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C208" t="s">
         <v>82</v>
@@ -2666,10 +2660,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B209" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C209" t="s">
         <v>82</v>
@@ -2677,10 +2671,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B210" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C210" t="s">
         <v>82</v>
@@ -2688,10 +2682,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B211" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C211" t="s">
         <v>82</v>
@@ -2699,10 +2693,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B212" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C212" t="s">
         <v>82</v>
@@ -2710,10 +2704,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B213" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C213" t="s">
         <v>82</v>
@@ -2721,10 +2715,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B214" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C214" t="s">
         <v>82</v>
@@ -2732,10 +2726,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B215" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C215" t="s">
         <v>82</v>
@@ -2743,10 +2737,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B216" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C216" t="s">
         <v>82</v>
@@ -2754,10 +2748,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B217" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C217" t="s">
         <v>82</v>
@@ -2765,10 +2759,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B218" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C218" t="s">
         <v>82</v>
@@ -2776,10 +2770,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B219" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C219" t="s">
         <v>82</v>
@@ -2787,10 +2781,10 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B220" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C220" t="s">
         <v>82</v>
@@ -2798,10 +2792,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B221" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C221" t="s">
         <v>82</v>
@@ -2809,10 +2803,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B222" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C222" t="s">
         <v>82</v>
@@ -2820,10 +2814,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B223" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C223" t="s">
         <v>82</v>
@@ -2831,10 +2825,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B224" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C224" t="s">
         <v>82</v>
@@ -2842,10 +2836,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B225" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C225" t="s">
         <v>82</v>
@@ -2853,10 +2847,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B226" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C226" t="s">
         <v>82</v>
@@ -2864,10 +2858,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B227" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C227" t="s">
         <v>82</v>
@@ -2875,10 +2869,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B228" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C228" t="s">
         <v>82</v>
@@ -2886,10 +2880,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B229" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C229" t="s">
         <v>82</v>
@@ -2897,10 +2891,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B230" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C230" t="s">
         <v>82</v>
@@ -2908,10 +2902,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C231" t="s">
         <v>82</v>
@@ -2919,10 +2913,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C232" t="s">
         <v>82</v>
@@ -2930,10 +2924,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B233" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C233" t="s">
         <v>82</v>
@@ -2941,10 +2935,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B234" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C234" t="s">
         <v>82</v>
@@ -2952,10 +2946,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B235" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C235" t="s">
         <v>82</v>
@@ -2963,10 +2957,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C236" t="s">
         <v>82</v>
@@ -2974,10 +2968,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B237" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C237" t="s">
         <v>82</v>
@@ -2985,10 +2979,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B238" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C238" t="s">
         <v>82</v>
@@ -2996,10 +2990,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C239" t="s">
         <v>82</v>
@@ -3007,10 +3001,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B240" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C240" t="s">
         <v>82</v>
@@ -3018,10 +3012,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B241" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C241" t="s">
         <v>82</v>
@@ -3029,10 +3023,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B242" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C242" t="s">
         <v>82</v>
@@ -3040,10 +3034,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B243" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C243" t="s">
         <v>82</v>
@@ -3051,10 +3045,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B244" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C244" t="s">
         <v>82</v>
@@ -3062,10 +3056,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B245" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C245" t="s">
         <v>82</v>
@@ -3073,10 +3067,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B246" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C246" t="s">
         <v>82</v>
@@ -3084,10 +3078,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B247" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C247" t="s">
         <v>82</v>
@@ -3095,10 +3089,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B248" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C248" t="s">
         <v>82</v>
@@ -3106,10 +3100,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B249" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C249" t="s">
         <v>82</v>
@@ -3117,10 +3111,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
+        <v>103</v>
+      </c>
+      <c r="B250" t="s">
         <v>107</v>
-      </c>
-      <c r="B250" t="s">
-        <v>111</v>
       </c>
       <c r="C250" t="s">
         <v>82</v>
@@ -3128,10 +3122,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B251" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C251" t="s">
         <v>82</v>
@@ -3139,10 +3133,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B252" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C252" t="s">
         <v>82</v>
@@ -3150,10 +3144,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B253" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C253" t="s">
         <v>82</v>
@@ -3161,10 +3155,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B254" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C254" t="s">
         <v>82</v>
@@ -3172,10 +3166,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B255" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C255" t="s">
         <v>82</v>
@@ -3183,10 +3177,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B256" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C256" t="s">
         <v>82</v>
@@ -3194,10 +3188,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B257" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C257" t="s">
         <v>82</v>
@@ -3205,10 +3199,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B258" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C258" t="s">
         <v>82</v>
@@ -3216,7 +3210,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B259" t="s">
         <v>37</v>
@@ -3227,7 +3221,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B260" t="s">
         <v>37</v>
@@ -3238,7 +3232,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B261" t="s">
         <v>37</v>
@@ -3249,7 +3243,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B262" t="s">
         <v>37</v>
@@ -3260,7 +3254,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B263" t="s">
         <v>37</v>
@@ -3271,7 +3265,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B264" t="s">
         <v>37</v>
@@ -3282,7 +3276,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B265" t="s">
         <v>37</v>
@@ -3293,7 +3287,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B266" t="s">
         <v>29</v>
@@ -3304,7 +3298,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B267" t="s">
         <v>47</v>
@@ -3315,7 +3309,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B268" t="s">
         <v>47</v>
@@ -3326,7 +3320,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B269" t="s">
         <v>47</v>
@@ -3337,7 +3331,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B270" t="s">
         <v>25</v>
@@ -3348,7 +3342,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B271" t="s">
         <v>26</v>
@@ -3359,7 +3353,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B272" t="s">
         <v>73</v>
@@ -3370,7 +3364,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B273" t="s">
         <v>73</v>
@@ -3381,7 +3375,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B274" t="s">
         <v>73</v>
@@ -3392,10 +3386,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B275" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C275" t="s">
         <v>82</v>
@@ -3403,10 +3397,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B276" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C276" t="s">
         <v>82</v>
@@ -3414,10 +3408,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B277" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C277" t="s">
         <v>82</v>
@@ -3425,10 +3419,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
+        <v>94</v>
+      </c>
+      <c r="B278" t="s">
         <v>98</v>
-      </c>
-      <c r="B278" t="s">
-        <v>102</v>
       </c>
       <c r="C278" t="s">
         <v>82</v>
@@ -3436,10 +3430,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B279" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C279" t="s">
         <v>82</v>
@@ -3447,10 +3441,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B280" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C280" t="s">
         <v>82</v>
@@ -3458,10 +3452,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B281" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C281" t="s">
         <v>82</v>
@@ -3469,10 +3463,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B282" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C282" t="s">
         <v>82</v>
@@ -3480,10 +3474,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B283" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C283" t="s">
         <v>82</v>
@@ -3491,10 +3485,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B284" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C284" t="s">
         <v>82</v>
@@ -3502,10 +3496,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B285" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C285" t="s">
         <v>82</v>
@@ -3513,10 +3507,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B286" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C286" t="s">
         <v>82</v>
@@ -3524,10 +3518,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B287" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C287" t="s">
         <v>82</v>
@@ -3535,10 +3529,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B288" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C288" t="s">
         <v>82</v>
@@ -3546,10 +3540,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B289" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C289" t="s">
         <v>82</v>
@@ -3557,10 +3551,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B290" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C290" t="s">
         <v>82</v>
@@ -3568,10 +3562,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
+        <v>95</v>
+      </c>
+      <c r="B291" t="s">
         <v>99</v>
-      </c>
-      <c r="B291" t="s">
-        <v>103</v>
       </c>
       <c r="C291" t="s">
         <v>82</v>
@@ -3579,10 +3573,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B292" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C292" t="s">
         <v>82</v>
@@ -3590,10 +3584,10 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B293" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C293" t="s">
         <v>82</v>
@@ -3601,10 +3595,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B294" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C294" t="s">
         <v>82</v>
@@ -3612,10 +3606,10 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B295" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C295" t="s">
         <v>82</v>
@@ -3623,10 +3617,10 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B296" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C296" t="s">
         <v>82</v>
@@ -3634,10 +3628,10 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B297" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C297" t="s">
         <v>82</v>
@@ -3645,10 +3639,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B298" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C298" t="s">
         <v>82</v>
@@ -3656,10 +3650,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B299" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C299" t="s">
         <v>82</v>
@@ -3667,10 +3661,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B300" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C300" t="s">
         <v>82</v>
@@ -3678,10 +3672,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B301" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C301" t="s">
         <v>82</v>
@@ -3689,10 +3683,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B302" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C302" t="s">
         <v>82</v>
@@ -3700,10 +3694,10 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
+        <v>96</v>
+      </c>
+      <c r="B303" t="s">
         <v>100</v>
-      </c>
-      <c r="B303" t="s">
-        <v>104</v>
       </c>
       <c r="C303" t="s">
         <v>82</v>
@@ -3711,10 +3705,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B304" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C304" t="s">
         <v>82</v>
@@ -3722,10 +3716,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B305" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C305" t="s">
         <v>82</v>
@@ -3733,10 +3727,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B306" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C306" t="s">
         <v>82</v>
@@ -3744,10 +3738,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B307" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C307" t="s">
         <v>82</v>
@@ -3755,10 +3749,10 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B308" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C308" t="s">
         <v>82</v>
@@ -3766,10 +3760,10 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B309" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C309" t="s">
         <v>82</v>
@@ -3777,10 +3771,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B310" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C310" t="s">
         <v>82</v>
@@ -3788,10 +3782,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B311" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C311" t="s">
         <v>82</v>
@@ -3799,10 +3793,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B312" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C312" t="s">
         <v>82</v>
@@ -3810,10 +3804,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B313" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C313" t="s">
         <v>82</v>
@@ -3821,10 +3815,10 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>97</v>
+      </c>
+      <c r="B314" t="s">
         <v>101</v>
-      </c>
-      <c r="B314" t="s">
-        <v>105</v>
       </c>
       <c r="C314" t="s">
         <v>82</v>
@@ -3832,10 +3826,10 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B315" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C315" t="s">
         <v>82</v>
@@ -3843,10 +3837,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B316" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C316" t="s">
         <v>82</v>
@@ -3854,10 +3848,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B317" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C317" t="s">
         <v>82</v>
@@ -3865,10 +3859,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B318" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C318" t="s">
         <v>82</v>
@@ -3876,10 +3870,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B319" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C319" t="s">
         <v>82</v>
@@ -3887,10 +3881,10 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B320" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C320" t="s">
         <v>82</v>
@@ -3898,10 +3892,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B321" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C321" t="s">
         <v>82</v>
@@ -3909,10 +3903,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B322" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C322" t="s">
         <v>82</v>
@@ -3920,10 +3914,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B323" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C323" t="s">
         <v>82</v>
@@ -3931,10 +3925,10 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
+        <v>98</v>
+      </c>
+      <c r="B324" t="s">
         <v>102</v>
-      </c>
-      <c r="B324" t="s">
-        <v>106</v>
       </c>
       <c r="C324" t="s">
         <v>82</v>
@@ -3942,10 +3936,10 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B325" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C325" t="s">
         <v>82</v>
@@ -3953,10 +3947,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B326" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C326" t="s">
         <v>82</v>
@@ -3964,10 +3958,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B327" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C327" t="s">
         <v>82</v>
@@ -3975,10 +3969,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B328" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C328" t="s">
         <v>82</v>
@@ -3986,10 +3980,10 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B329" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C329" t="s">
         <v>82</v>
@@ -3997,10 +3991,10 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B330" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C330" t="s">
         <v>82</v>
@@ -4008,10 +4002,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B331" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C331" t="s">
         <v>82</v>
@@ -4019,10 +4013,10 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B332" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C332" t="s">
         <v>82</v>
@@ -4030,10 +4024,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B333" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C333" t="s">
         <v>82</v>
@@ -4041,10 +4035,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B334" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C334" t="s">
         <v>82</v>
@@ -4052,10 +4046,10 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>99</v>
+      </c>
+      <c r="B335" t="s">
         <v>103</v>
-      </c>
-      <c r="B335" t="s">
-        <v>107</v>
       </c>
       <c r="C335" t="s">
         <v>82</v>
@@ -4063,10 +4057,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B336" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C336" t="s">
         <v>82</v>
@@ -4074,10 +4068,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B337" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C337" t="s">
         <v>82</v>
@@ -4085,10 +4079,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B338" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C338" t="s">
         <v>82</v>
@@ -4096,10 +4090,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B339" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C339" t="s">
         <v>82</v>
@@ -4107,10 +4101,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B340" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C340" t="s">
         <v>82</v>
@@ -4118,10 +4112,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>100</v>
+      </c>
+      <c r="B341" t="s">
         <v>104</v>
-      </c>
-      <c r="B341" t="s">
-        <v>108</v>
       </c>
       <c r="C341" t="s">
         <v>82</v>
@@ -4129,10 +4123,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B342" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C342" t="s">
         <v>82</v>
@@ -4140,10 +4134,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B343" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C343" t="s">
         <v>82</v>
@@ -4151,10 +4145,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B344" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C344" t="s">
         <v>82</v>
@@ -4162,10 +4156,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B345" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C345" t="s">
         <v>82</v>
@@ -4173,10 +4167,10 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B346" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C346" t="s">
         <v>82</v>
@@ -4184,10 +4178,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B347" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C347" t="s">
         <v>82</v>
@@ -4195,10 +4189,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B348" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C348" t="s">
         <v>82</v>
@@ -4206,10 +4200,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
+        <v>101</v>
+      </c>
+      <c r="B349" t="s">
         <v>105</v>
-      </c>
-      <c r="B349" t="s">
-        <v>109</v>
       </c>
       <c r="C349" t="s">
         <v>82</v>
@@ -4217,10 +4211,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B350" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C350" t="s">
         <v>82</v>
@@ -4228,10 +4222,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B351" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C351" t="s">
         <v>82</v>
@@ -4239,10 +4233,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B352" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C352" t="s">
         <v>82</v>
@@ -4250,10 +4244,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B353" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C353" t="s">
         <v>82</v>
@@ -4261,10 +4255,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B354" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C354" t="s">
         <v>82</v>
@@ -4272,10 +4266,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
+        <v>102</v>
+      </c>
+      <c r="B355" t="s">
         <v>106</v>
-      </c>
-      <c r="B355" t="s">
-        <v>110</v>
       </c>
       <c r="C355" t="s">
         <v>82</v>
@@ -4283,10 +4277,10 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B356" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C356" t="s">
         <v>82</v>
@@ -4294,10 +4288,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B357" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C357" t="s">
         <v>82</v>
@@ -4305,10 +4299,10 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B358" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C358" t="s">
         <v>82</v>
@@ -4316,10 +4310,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B359" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C359" t="s">
         <v>82</v>
@@ -4327,10 +4321,10 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B360" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C360" t="s">
         <v>82</v>
@@ -4338,10 +4332,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B361" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C361" t="s">
         <v>82</v>
@@ -4349,10 +4343,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B362" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C362" t="s">
         <v>82</v>
@@ -4360,10 +4354,10 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B363" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C363" t="s">
         <v>82</v>
@@ -4371,10 +4365,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B364" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C364" t="s">
         <v>82</v>
@@ -4382,10 +4376,10 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B365" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C365" t="s">
         <v>82</v>
@@ -4396,7 +4390,7 @@
         <v>37</v>
       </c>
       <c r="B366" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C366" t="s">
         <v>82</v>
@@ -4407,7 +4401,7 @@
         <v>37</v>
       </c>
       <c r="B367" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C367" t="s">
         <v>82</v>
@@ -4418,7 +4412,7 @@
         <v>37</v>
       </c>
       <c r="B368" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C368" t="s">
         <v>82</v>
@@ -4429,7 +4423,7 @@
         <v>37</v>
       </c>
       <c r="B369" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C369" t="s">
         <v>82</v>
@@ -4440,7 +4434,7 @@
         <v>37</v>
       </c>
       <c r="B370" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C370" t="s">
         <v>82</v>
@@ -4451,7 +4445,7 @@
         <v>37</v>
       </c>
       <c r="B371" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C371" t="s">
         <v>82</v>
@@ -4462,7 +4456,7 @@
         <v>37</v>
       </c>
       <c r="B372" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C372" t="s">
         <v>82</v>
@@ -4473,7 +4467,7 @@
         <v>29</v>
       </c>
       <c r="B373" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C373" t="s">
         <v>82</v>
@@ -4484,7 +4478,7 @@
         <v>47</v>
       </c>
       <c r="B374" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C374" t="s">
         <v>82</v>
@@ -4495,7 +4489,7 @@
         <v>47</v>
       </c>
       <c r="B375" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C375" t="s">
         <v>82</v>
@@ -4506,7 +4500,7 @@
         <v>47</v>
       </c>
       <c r="B376" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C376" t="s">
         <v>82</v>
@@ -4517,7 +4511,7 @@
         <v>25</v>
       </c>
       <c r="B377" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C377" t="s">
         <v>82</v>
@@ -4528,7 +4522,7 @@
         <v>26</v>
       </c>
       <c r="B378" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C378" t="s">
         <v>82</v>
@@ -4539,7 +4533,7 @@
         <v>73</v>
       </c>
       <c r="B379" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C379" t="s">
         <v>82</v>
@@ -4550,7 +4544,7 @@
         <v>73</v>
       </c>
       <c r="B380" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C380" t="s">
         <v>82</v>
@@ -4561,7 +4555,7 @@
         <v>73</v>
       </c>
       <c r="B381" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C381" t="s">
         <v>82</v>
@@ -4569,7 +4563,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B382" t="s">
         <v>29</v>
@@ -4583,7 +4577,7 @@
         <v>29</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C383" t="s">
         <v>82</v>
@@ -4597,7 +4591,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCB1B3A-FF7E-418A-ACDC-43A407A50999}">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="36" width="23.1640625" customWidth="1"/>
@@ -4916,18 +4910,18 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -4935,7 +4929,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -4943,7 +4937,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -4951,7 +4945,7 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -4959,20 +4953,20 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
@@ -4980,10 +4974,10 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -4991,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -4999,20 +4993,20 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
@@ -5020,47 +5014,47 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -5068,23 +5062,23 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
         <v>59</v>
@@ -5092,26 +5086,26 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -5119,7 +5113,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -5127,7 +5121,7 @@
         <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -5135,20 +5129,20 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
         <v>93</v>
@@ -5156,56 +5150,24 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>36</v>
-      </c>
-      <c r="B69" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>25</v>
-      </c>
-      <c r="B70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>26</v>
-      </c>
-      <c r="B71" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>36</v>
-      </c>
-      <c r="B72" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B69" xr:uid="{42A05C29-4194-4F5B-9F50-348A542B684D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B70:B73">
-    <sortCondition ref="B70:B73"/>
+  <autoFilter ref="A1:B68" xr:uid="{42A05C29-4194-4F5B-9F50-348A542B684D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B69">
+    <sortCondition ref="B69"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5213,7 +5175,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B6FDF4-9CFC-43D7-A608-94B069C0D72B}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
@@ -5535,31 +5497,31 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
         <v>59</v>
@@ -5567,15 +5529,15 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
@@ -5583,7 +5545,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
@@ -5591,15 +5553,15 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
@@ -5607,7 +5569,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
         <v>21</v>
@@ -5615,15 +5577,15 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
@@ -5631,49 +5593,34 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
         <v>93</v>
       </c>
-      <c r="B51" t="s">
-        <v>93</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B51" xr:uid="{6257D8A0-3C51-429D-B528-47EE622101B0}"/>
+  <autoFilter ref="A1:B50" xr:uid="{6257D8A0-3C51-429D-B528-47EE622101B0}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A25A5DE-FBC9-C14F-BE79-A9083EDDE5F7}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5688,7 +5635,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -5773,7 +5720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB13D4-1EC2-4E93-9F61-BAB11C15D590}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
@@ -5861,21 +5808,16 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5886,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01359C4D-64DE-47F4-B41D-DB468090306F}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -6081,7 +6023,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>93</v>
@@ -6089,36 +6031,31 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
         <v>93</v>
       </c>
     </row>
@@ -6514,6 +6451,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E6F967323C0D5D438811C071A0F9DCC2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00e16cf4f371becfd4fa90a69a8084a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d8af0d66-b3db-4c81-87bc-15f9b72a49e2" xmlns:ns3="c1406b29-91bf-464c-9cd2-26ba5eb06139" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b473d16828d8fcef31f33e0797a9447b" ns2:_="" ns3:_="">
     <xsd:import namespace="d8af0d66-b3db-4c81-87bc-15f9b72a49e2"/>
@@ -6710,15 +6656,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6731,6 +6668,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07E255A9-C5C8-415F-8913-E47EE92CF771}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99E1D978-286A-4C40-8DCC-8CC98108374E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6745,14 +6690,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07E255A9-C5C8-415F-8913-E47EE92CF771}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
